--- a/erp-server/erp-server-plm/src/main/resources/excel/bomInfoError.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/bomInfoError.xlsx
@@ -97,19 +97,19 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>${.typeName}</t>
+    <t>{.typeName}</t>
   </si>
   <si>
-    <t>${.parentSku}</t>
+    <t>{.parentSku}</t>
   </si>
   <si>
-    <t>${.childSku}</t>
+    <t>{.childSku}</t>
   </si>
   <si>
-    <t>${.quantityStr}</t>
+    <t>{.quantityStr}</t>
   </si>
   <si>
-    <t>${.errorMsg}</t>
+    <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
